--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -56,10 +56,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>172.31.183.49</t>
+    <t>172.31.44.172</t>
   </si>
   <si>
-    <t>8.221.119.18</t>
+    <t>34.220.221.8</t>
   </si>
 </sst>
 </file>
@@ -1117,7 +1117,7 @@
       <c r="D6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="3">

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -56,10 +56,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>172.31.44.172</t>
+    <t>172.31.21.19</t>
   </si>
   <si>
-    <t>34.220.221.8</t>
+    <t>98.84.156.7</t>
   </si>
 </sst>
 </file>
@@ -692,7 +692,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -706,9 +706,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1114,10 +1111,10 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="3">

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -59,7 +59,7 @@
     <t>172.31.21.19</t>
   </si>
   <si>
-    <t>98.84.156.7</t>
+    <t>23.20.18.54</t>
   </si>
 </sst>
 </file>

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -56,10 +56,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>172.31.21.19</t>
+    <t>172.20.250.253</t>
   </si>
   <si>
-    <t>23.20.18.54</t>
+    <t>47.251.252.96</t>
   </si>
 </sst>
 </file>

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -56,10 +56,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>172.20.250.253</t>
+    <t>172.20.227.82</t>
   </si>
   <si>
-    <t>47.251.252.96</t>
+    <t>47.86.59.101</t>
   </si>
 </sst>
 </file>
@@ -1111,10 +1111,10 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="3">

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -56,10 +56,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>172.20.227.82</t>
+    <t>172.20.250.253</t>
   </si>
   <si>
-    <t>47.86.59.101</t>
+    <t>47.251.252.96</t>
   </si>
 </sst>
 </file>

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -56,10 +56,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>172.20.250.253</t>
+    <t>172.31.21.19</t>
   </si>
   <si>
-    <t>47.251.252.96</t>
+    <t>23.20.18.54</t>
   </si>
 </sst>
 </file>

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -56,10 +56,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>172.31.21.19</t>
+    <t>172.20.227.82</t>
   </si>
   <si>
-    <t>23.20.18.54</t>
+    <t>47.86.59.101</t>
   </si>
 </sst>
 </file>

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -56,10 +56,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>172.20.227.82</t>
+    <t>172.20.250.253</t>
   </si>
   <si>
-    <t>47.86.59.101</t>
+    <t>47.77.221.152</t>
   </si>
 </sst>
 </file>

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -56,10 +56,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>172.20.250.253</t>
+    <t>172.31.183.54</t>
   </si>
   <si>
-    <t>47.77.221.152</t>
+    <t>8.221.110.80</t>
   </si>
 </sst>
 </file>

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -56,10 +56,10 @@
     <t>string</t>
   </si>
   <si>
-    <t>172.31.183.54</t>
+    <t>172.20.250.253</t>
   </si>
   <si>
-    <t>8.221.110.80</t>
+    <t>47.77.221.152</t>
   </si>
 </sst>
 </file>

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
   <si>
     <t>Id</t>
   </si>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>172.31.183.54</t>
+  </si>
+  <si>
+    <t>8.221.110.80</t>
   </si>
   <si>
     <t>172.20.250.253</t>
@@ -1055,8 +1061,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:F6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="5"/>
+  <dimension ref="C3:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="21.125" style="1" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
@@ -1121,6 +1127,14 @@
         <v>20302</v>
       </c>
     </row>
+    <row r="8" spans="3:6">
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.699305555555556" right="0.699305555555556" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
+++ b/Excel/StartConfig/Google/StartMachineConfig@s.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="15">
   <si>
     <t>Id</t>
   </si>
@@ -54,6 +54,12 @@
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>172.20.227.82</t>
+  </si>
+  <si>
+    <t>47.86.59.101</t>
   </si>
   <si>
     <t>172.31.183.54</t>
@@ -1127,12 +1133,20 @@
         <v>20302</v>
       </c>
     </row>
+    <row r="7" spans="3:6">
+      <c r="D7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
     <row r="8" spans="3:6">
       <c r="D8" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
